--- a/doc/_static/example-files/PMHC-MDS-Survey-1-0.xlsx
+++ b/doc/_static/example-files/PMHC-MDS-Survey-1-0.xlsx
@@ -1,18 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennib/Work/git/PMHC/spec-survey/doc/_static/example-files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D74E0D-5C1C-E44C-9D95-9501A8E19148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
     <sheet name="Organisations" sheetId="2" r:id="rId2"/>
     <sheet name="Surveys" sheetId="3" r:id="rId3"/>
-    <sheet name="YES PHN" sheetId="4" r:id="rId4"/>
+    <sheet name="YES-PHN" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -241,8 +247,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,13 +285,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -323,7 +337,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -357,6 +371,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -391,9 +406,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -566,11 +582,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -578,7 +594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -586,7 +602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -600,11 +616,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -636,7 +652,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -662,7 +678,7 @@
         <v>9099999</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -694,11 +710,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -712,7 +728,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -726,7 +742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -743,11 +759,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AI4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -854,7 +870,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -949,7 +965,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1050,7 +1066,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
